--- a/MDE_Materii_Prime_Preturi.xlsx
+++ b/MDE_Materii_Prime_Preturi.xlsx
@@ -1148,7 +1148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L239"/>
+  <dimension ref="A1:L401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="140" min="1" max="1"/>
@@ -13928,6 +13928,8546 @@
           <t>MOQ = piese dintr-un log</t>
         </is>
       </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B240" s="29" t="inlineStr">
+        <is>
+          <t>Norbond A7300</t>
+        </is>
+      </c>
+      <c r="C240" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D240" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E240" s="28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F240" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G240" s="86" t="n">
+        <v>31</v>
+      </c>
+      <c r="H240" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I240" s="28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J240" s="31" t="inlineStr"/>
+      <c r="K240" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2767 Amusnet</t>
+        </is>
+      </c>
+      <c r="L240" s="33" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B241" s="29" t="inlineStr">
+        <is>
+          <t>Norbond A7500</t>
+        </is>
+      </c>
+      <c r="C241" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D241" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E241" s="28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F241" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G241" s="86" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="H241" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I241" s="28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J241" s="31" t="inlineStr"/>
+      <c r="K241" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2767 Amusnet</t>
+        </is>
+      </c>
+      <c r="L241" s="33" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B242" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Safety-Walk™ 710 Black</t>
+        </is>
+      </c>
+      <c r="C242" s="28" t="n">
+        <v>305</v>
+      </c>
+      <c r="D242" s="28" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="E242" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F242" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G242" s="86" t="n">
+        <v>68</v>
+      </c>
+      <c r="H242" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I242" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J242" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K242" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2772</t>
+        </is>
+      </c>
+      <c r="L242" s="33" t="inlineStr">
+        <is>
+          <t>slip resistant coarse</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B243" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Bumpon™ Rollstock SJ6216 Black R25FL</t>
+        </is>
+      </c>
+      <c r="C243" s="28" t="n">
+        <v>114</v>
+      </c>
+      <c r="D243" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E243" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F243" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G243" s="86" t="n">
+        <v>126</v>
+      </c>
+      <c r="H243" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I243" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J243" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K243" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2782 EJOT</t>
+        </is>
+      </c>
+      <c r="L243" s="33" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B244" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Bumpon™ Rollstock SJ5616 Clear A20FL</t>
+        </is>
+      </c>
+      <c r="C244" s="28" t="n">
+        <v>114</v>
+      </c>
+      <c r="D244" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E244" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F244" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G244" s="86" t="n">
+        <v>181</v>
+      </c>
+      <c r="H244" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I244" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J244" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K244" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2782 EJOT</t>
+        </is>
+      </c>
+      <c r="L244" s="33" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B245" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TESA 62508</t>
+        </is>
+      </c>
+      <c r="C245" s="28" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D245" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="E245" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F245" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G245" s="86" t="n">
+        <v>8</v>
+      </c>
+      <c r="H245" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I245" s="28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J245" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K245" s="32" t="inlineStr">
+        <is>
+          <t>PRJM 2758 Magna</t>
+        </is>
+      </c>
+      <c r="L245" s="33" t="inlineStr">
+        <is>
+          <t>pret redus de la 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B246" s="29" t="inlineStr">
+        <is>
+          <t>FOLIE 24S56W</t>
+        </is>
+      </c>
+      <c r="C246" s="28" t="n">
+        <v>1219</v>
+      </c>
+      <c r="D246" s="28" t="n">
+        <v>305</v>
+      </c>
+      <c r="E246" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F246" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G246" s="86" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H246" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I246" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J246" s="31" t="inlineStr"/>
+      <c r="K246" s="32" t="inlineStr">
+        <is>
+          <t>PRJM 2768 Magna</t>
+        </is>
+      </c>
+      <c r="L246" s="33" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B247" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TESA 50530</t>
+        </is>
+      </c>
+      <c r="C247" s="28" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D247" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="E247" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F247" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G247" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="H247" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I247" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J247" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K247" s="32" t="inlineStr">
+        <is>
+          <t>PRJM 2768 Magna</t>
+        </is>
+      </c>
+      <c r="L247" s="33" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B248" s="29" t="inlineStr">
+        <is>
+          <t>D41170</t>
+        </is>
+      </c>
+      <c r="C248" s="28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D248" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E248" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F248" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G248" s="86" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H248" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I248" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J248" s="31" t="inlineStr">
+        <is>
+          <t>Neveon</t>
+        </is>
+      </c>
+      <c r="K248" s="32" t="inlineStr">
+        <is>
+          <t>RFQ_005_247</t>
+        </is>
+      </c>
+      <c r="L248" s="33" t="inlineStr">
+        <is>
+          <t>2000×1000×10mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B249" s="29" t="inlineStr">
+        <is>
+          <t>FELT HDF B2120 250G/M2</t>
+        </is>
+      </c>
+      <c r="C249" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D249" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E249" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F249" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G249" s="86" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H249" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I249" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J249" s="31" t="inlineStr"/>
+      <c r="K249" s="32" t="inlineStr">
+        <is>
+          <t>RFQ_005_247</t>
+        </is>
+      </c>
+      <c r="L249" s="33" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B250" s="29" t="inlineStr">
+        <is>
+          <t>PU FOAM D30130M</t>
+        </is>
+      </c>
+      <c r="C250" s="28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D250" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E250" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="F250" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G250" s="86" t="n">
+        <v>7</v>
+      </c>
+      <c r="H250" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I250" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J250" s="31" t="inlineStr">
+        <is>
+          <t>Neveon</t>
+        </is>
+      </c>
+      <c r="K250" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2774 Fritzmeier</t>
+        </is>
+      </c>
+      <c r="L250" s="33" t="inlineStr">
+        <is>
+          <t>2000×1000×30mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B251" s="29" t="inlineStr">
+        <is>
+          <t>PU FOAM D30130M</t>
+        </is>
+      </c>
+      <c r="C251" s="28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D251" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E251" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="F251" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G251" s="86" t="n">
+        <v>14</v>
+      </c>
+      <c r="H251" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I251" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J251" s="31" t="inlineStr">
+        <is>
+          <t>Neveon</t>
+        </is>
+      </c>
+      <c r="K251" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2774 Fritzmeier</t>
+        </is>
+      </c>
+      <c r="L251" s="33" t="inlineStr">
+        <is>
+          <t>var. 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B252" s="29" t="inlineStr">
+        <is>
+          <t>PU FOAM D30130M</t>
+        </is>
+      </c>
+      <c r="C252" s="28" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D252" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E252" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="F252" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G252" s="86" t="n">
+        <v>7</v>
+      </c>
+      <c r="H252" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I252" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J252" s="31" t="inlineStr">
+        <is>
+          <t>Neveon</t>
+        </is>
+      </c>
+      <c r="K252" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2774 Fritzmeier</t>
+        </is>
+      </c>
+      <c r="L252" s="33" t="inlineStr">
+        <is>
+          <t>1300×1000×30mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B253" s="29" t="inlineStr">
+        <is>
+          <t>PU FOAM D30130M</t>
+        </is>
+      </c>
+      <c r="C253" s="28" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D253" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E253" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F253" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G253" s="86" t="n">
+        <v>12</v>
+      </c>
+      <c r="H253" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I253" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J253" s="31" t="inlineStr">
+        <is>
+          <t>Neveon</t>
+        </is>
+      </c>
+      <c r="K253" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2774 Fritzmeier</t>
+        </is>
+      </c>
+      <c r="L253" s="33" t="inlineStr">
+        <is>
+          <t>1300×1000×50mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B254" s="29" t="inlineStr">
+        <is>
+          <t>FOLIE A360CL</t>
+        </is>
+      </c>
+      <c r="C254" s="28" t="n">
+        <v>400</v>
+      </c>
+      <c r="D254" s="28" t="n">
+        <v>250</v>
+      </c>
+      <c r="E254" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F254" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G254" s="86" t="n">
+        <v>212</v>
+      </c>
+      <c r="H254" s="28" t="inlineStr">
+        <is>
+          <t>€/buc</t>
+        </is>
+      </c>
+      <c r="I254" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J254" s="31" t="inlineStr"/>
+      <c r="K254" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2776 Antalis</t>
+        </is>
+      </c>
+      <c r="L254" s="33" t="inlineStr">
+        <is>
+          <t>folie electrostatica; in stoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B255" s="29" t="inlineStr">
+        <is>
+          <t>Packtape 23my acryl transparent</t>
+        </is>
+      </c>
+      <c r="C255" s="28" t="n">
+        <v>48</v>
+      </c>
+      <c r="D255" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="E255" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F255" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G255" s="86" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="H255" s="28" t="inlineStr">
+        <is>
+          <t>€/rolă</t>
+        </is>
+      </c>
+      <c r="I255" s="28" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="J255" s="31" t="inlineStr"/>
+      <c r="K255" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2778 PGS</t>
+        </is>
+      </c>
+      <c r="L255" s="33" t="inlineStr">
+        <is>
+          <t>banda ambalare; 4-5 sapt</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="28" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B256" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Double Coated Tape GPT-020TF Transparent</t>
+        </is>
+      </c>
+      <c r="C256" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="D256" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="E256" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F256" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G256" s="86" t="n">
+        <v>2707</v>
+      </c>
+      <c r="H256" s="28" t="inlineStr">
+        <is>
+          <t>€/rolă</t>
+        </is>
+      </c>
+      <c r="I256" s="28" t="inlineStr">
+        <is>
+          <t>3 role</t>
+        </is>
+      </c>
+      <c r="J256" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K256" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2781</t>
+        </is>
+      </c>
+      <c r="L256" s="33" t="inlineStr">
+        <is>
+          <t>Red Liner; 6-8 sapt</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B257" s="29" t="inlineStr">
+        <is>
+          <t>3M™ PX5008</t>
+        </is>
+      </c>
+      <c r="C257" s="28" t="n">
+        <v>111</v>
+      </c>
+      <c r="D257" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E257" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F257" s="28" t="inlineStr">
+        <is>
+          <t>buc</t>
+        </is>
+      </c>
+      <c r="G257" s="86" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="H257" s="28" t="inlineStr">
+        <is>
+          <t>€/buc</t>
+        </is>
+      </c>
+      <c r="I257" s="28" t="inlineStr">
+        <is>
+          <t>6500 buc</t>
+        </is>
+      </c>
+      <c r="J257" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K257" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2784 Bentley</t>
+        </is>
+      </c>
+      <c r="L257" s="33" t="inlineStr">
+        <is>
+          <t>pret/piesa; 111×10×0.8mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B258" s="29" t="inlineStr">
+        <is>
+          <t>Toray Airlite 180 g/m²</t>
+        </is>
+      </c>
+      <c r="C258" s="28" t="n">
+        <v>925</v>
+      </c>
+      <c r="D258" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E258" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F258" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G258" s="86" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H258" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I258" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J258" s="31" t="inlineStr">
+        <is>
+          <t>Toray</t>
+        </is>
+      </c>
+      <c r="K258" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2785 Ford</t>
+        </is>
+      </c>
+      <c r="L258" s="33" t="inlineStr">
+        <is>
+          <t>1000×50m</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B259" s="29" t="inlineStr">
+        <is>
+          <t>PORON 4790-79-12 3.5mm</t>
+        </is>
+      </c>
+      <c r="C259" s="28" t="n">
+        <v>300</v>
+      </c>
+      <c r="D259" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E259" s="28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F259" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G259" s="86" t="n">
+        <v>45</v>
+      </c>
+      <c r="H259" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I259" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J259" s="31" t="inlineStr">
+        <is>
+          <t>Rogers</t>
+        </is>
+      </c>
+      <c r="K259" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2788 SHRO</t>
+        </is>
+      </c>
+      <c r="L259" s="33" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B260" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TESA 4982</t>
+        </is>
+      </c>
+      <c r="C260" s="28" t="n">
+        <v>1372</v>
+      </c>
+      <c r="D260" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="E260" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F260" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G260" s="86" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H260" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I260" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J260" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K260" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2788 SHRO</t>
+        </is>
+      </c>
+      <c r="L260" s="33" t="inlineStr">
+        <is>
+          <t>adeziv</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B261" s="29" t="inlineStr">
+        <is>
+          <t>NITTO SPV9330 TRANSPARENT</t>
+        </is>
+      </c>
+      <c r="C261" s="28" t="n">
+        <v>1260</v>
+      </c>
+      <c r="D261" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="E261" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F261" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G261" s="86" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H261" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I261" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J261" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K261" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2792 META</t>
+        </is>
+      </c>
+      <c r="L261" s="33" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B262" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Double Coated Tape GPT-020 Transparent</t>
+        </is>
+      </c>
+      <c r="C262" s="28" t="n">
+        <v>1540</v>
+      </c>
+      <c r="D262" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E262" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F262" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G262" s="86" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="H262" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I262" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J262" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K262" s="32" t="inlineStr">
+        <is>
+          <t>Ciocorom P2W2</t>
+        </is>
+      </c>
+      <c r="L262" s="33" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B263" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TESA 51136</t>
+        </is>
+      </c>
+      <c r="C263" s="28" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D263" s="28" t="n">
+        <v>330</v>
+      </c>
+      <c r="E263" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F263" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G263" s="86" t="n">
+        <v>925</v>
+      </c>
+      <c r="H263" s="28" t="inlineStr">
+        <is>
+          <t>€/log</t>
+        </is>
+      </c>
+      <c r="I263" s="28" t="inlineStr">
+        <is>
+          <t>1 log</t>
+        </is>
+      </c>
+      <c r="J263" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K263" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2794 AMBAFOL</t>
+        </is>
+      </c>
+      <c r="L263" s="33" t="inlineStr">
+        <is>
+          <t>pret/log; stoc 6 log</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B264" s="29" t="inlineStr">
+        <is>
+          <t>FOLIE PF22 RC BLUE</t>
+        </is>
+      </c>
+      <c r="C264" s="28" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D264" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="E264" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F264" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G264" s="86" t="n">
+        <v>532</v>
+      </c>
+      <c r="H264" s="28" t="inlineStr">
+        <is>
+          <t>€/rolă</t>
+        </is>
+      </c>
+      <c r="I264" s="28" t="inlineStr">
+        <is>
+          <t>20 role</t>
+        </is>
+      </c>
+      <c r="J264" s="31" t="inlineStr"/>
+      <c r="K264" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2794 AMBAFOL</t>
+        </is>
+      </c>
+      <c r="L264" s="33" t="inlineStr">
+        <is>
+          <t>6-8 sapt</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B265" s="29" t="inlineStr">
+        <is>
+          <t>Nitto EE-1010 TH15</t>
+        </is>
+      </c>
+      <c r="C265" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D265" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="E265" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="F265" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G265" s="86" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="H265" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I265" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J265" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K265" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2786 excenter</t>
+        </is>
+      </c>
+      <c r="L265" s="33" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B266" s="29" t="inlineStr">
+        <is>
+          <t>FOLIE 2104C</t>
+        </is>
+      </c>
+      <c r="C266" s="28" t="n">
+        <v>1219</v>
+      </c>
+      <c r="D266" s="28" t="n">
+        <v>305</v>
+      </c>
+      <c r="E266" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F266" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G266" s="86" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H266" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I266" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J266" s="31" t="inlineStr"/>
+      <c r="K266" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2801 Matikon</t>
+        </is>
+      </c>
+      <c r="L266" s="33" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B267" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TESA 51136</t>
+        </is>
+      </c>
+      <c r="C267" s="28" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D267" s="28" t="n">
+        <v>330</v>
+      </c>
+      <c r="E267" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F267" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G267" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="H267" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I267" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J267" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K267" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2802 conectori</t>
+        </is>
+      </c>
+      <c r="L267" s="33" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B268" s="29" t="inlineStr">
+        <is>
+          <t>Felt X12</t>
+        </is>
+      </c>
+      <c r="C268" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D268" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E268" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F268" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G268" s="86" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H268" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I268" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J268" s="31" t="inlineStr"/>
+      <c r="K268" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2803 MGA</t>
+        </is>
+      </c>
+      <c r="L268" s="33" t="inlineStr">
+        <is>
+          <t>cercuri</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B269" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TRANSLINK TL50LE20</t>
+        </is>
+      </c>
+      <c r="C269" s="28" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D269" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="E269" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F269" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G269" s="86" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H269" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I269" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J269" s="31" t="inlineStr"/>
+      <c r="K269" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2803 MGA</t>
+        </is>
+      </c>
+      <c r="L269" s="33" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B270" s="29" t="inlineStr">
+        <is>
+          <t>EPDM 12-45 2mm</t>
+        </is>
+      </c>
+      <c r="C270" s="28" t="n">
+        <v>1330</v>
+      </c>
+      <c r="D270" s="28" t="n">
+        <v>700</v>
+      </c>
+      <c r="E270" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F270" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G270" s="86" t="n">
+        <v>17</v>
+      </c>
+      <c r="H270" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I270" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J270" s="31" t="inlineStr">
+        <is>
+          <t>Interep</t>
+        </is>
+      </c>
+      <c r="K270" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2806 EKI 350 NBR</t>
+        </is>
+      </c>
+      <c r="L270" s="33" t="inlineStr">
+        <is>
+          <t>1330×700×2mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B271" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Acrylic Foam Tape PX5005F Gray 0.5mm</t>
+        </is>
+      </c>
+      <c r="C271" s="28" t="n">
+        <v>1230</v>
+      </c>
+      <c r="D271" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E271" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F271" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G271" s="86" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="H271" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I271" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J271" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K271" s="32" t="inlineStr">
+        <is>
+          <t>Proiect Dourdin</t>
+        </is>
+      </c>
+      <c r="L271" s="33" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B272" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Die-Cuttable Tape DC2005S2 Black</t>
+        </is>
+      </c>
+      <c r="C272" s="28" t="n">
+        <v>1168</v>
+      </c>
+      <c r="D272" s="28" t="n">
+        <v>160</v>
+      </c>
+      <c r="E272" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F272" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G272" s="86" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="H272" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I272" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J272" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K272" s="32" t="inlineStr">
+        <is>
+          <t>Proiect Dourdin</t>
+        </is>
+      </c>
+      <c r="L272" s="33" t="inlineStr">
+        <is>
+          <t>20 mil</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B273" s="29" t="inlineStr">
+        <is>
+          <t>NITTO 9310 FILM</t>
+        </is>
+      </c>
+      <c r="C273" s="28" t="n">
+        <v>1540</v>
+      </c>
+      <c r="D273" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="E273" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F273" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G273" s="86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H273" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I273" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J273" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K273" s="32" t="inlineStr">
+        <is>
+          <t>PRJM 2524 Kostal</t>
+        </is>
+      </c>
+      <c r="L273" s="33" t="inlineStr">
+        <is>
+          <t>folie protectie</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B274" s="29" t="inlineStr">
+        <is>
+          <t>3M 3812</t>
+        </is>
+      </c>
+      <c r="C274" s="28" t="n">
+        <v>152</v>
+      </c>
+      <c r="D274" s="28" t="n">
+        <v>508</v>
+      </c>
+      <c r="E274" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F274" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G274" s="86" t="n">
+        <v>29</v>
+      </c>
+      <c r="H274" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I274" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J274" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K274" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2799 Repex</t>
+        </is>
+      </c>
+      <c r="L274" s="33" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B275" s="29" t="inlineStr">
+        <is>
+          <t>RR T 4545 D X FL BLK</t>
+        </is>
+      </c>
+      <c r="C275" s="28" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D275" s="28" t="n">
+        <v>140</v>
+      </c>
+      <c r="E275" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F275" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G275" s="86" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="H275" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I275" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J275" s="31" t="inlineStr">
+        <is>
+          <t>Neveon</t>
+        </is>
+      </c>
+      <c r="K275" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2744 Fuerda</t>
+        </is>
+      </c>
+      <c r="L275" s="33" t="inlineStr">
+        <is>
+          <t>art.1300010559</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B276" s="29" t="inlineStr">
+        <is>
+          <t>AFTC AM1208</t>
+        </is>
+      </c>
+      <c r="C276" s="28" t="n">
+        <v>900</v>
+      </c>
+      <c r="D276" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E276" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F276" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G276" s="86" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="H276" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I276" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J276" s="31" t="inlineStr">
+        <is>
+          <t>AFTC</t>
+        </is>
+      </c>
+      <c r="K276" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2769 Plastor</t>
+        </is>
+      </c>
+      <c r="L276" s="33" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B277" s="29" t="inlineStr">
+        <is>
+          <t>Toray Airlite 180 15mm</t>
+        </is>
+      </c>
+      <c r="C277" s="28" t="n">
+        <v>925</v>
+      </c>
+      <c r="D277" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="E277" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="F277" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G277" s="86" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H277" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I277" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J277" s="31" t="inlineStr">
+        <is>
+          <t>Toray</t>
+        </is>
+      </c>
+      <c r="K277" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2785 Ford</t>
+        </is>
+      </c>
+      <c r="L277" s="33" t="inlineStr">
+        <is>
+          <t>acustic</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B278" s="29" t="inlineStr">
+        <is>
+          <t>PORON 4790-92-09039-04-54T</t>
+        </is>
+      </c>
+      <c r="C278" s="28" t="n">
+        <v>1372</v>
+      </c>
+      <c r="D278" s="28" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="E278" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F278" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G278" s="86" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="H278" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I278" s="28" t="inlineStr">
+        <is>
+          <t>250.8 mp</t>
+        </is>
+      </c>
+      <c r="J278" s="31" t="inlineStr">
+        <is>
+          <t>Rogers</t>
+        </is>
+      </c>
+      <c r="K278" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2807</t>
+        </is>
+      </c>
+      <c r="L278" s="33" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B279" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TESA 4982</t>
+        </is>
+      </c>
+      <c r="C279" s="28" t="n">
+        <v>1372</v>
+      </c>
+      <c r="D279" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="E279" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F279" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G279" s="86" t="n">
+        <v>7</v>
+      </c>
+      <c r="H279" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I279" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J279" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K279" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2807</t>
+        </is>
+      </c>
+      <c r="L279" s="33" t="inlineStr">
+        <is>
+          <t>adeziv</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B280" s="29" t="inlineStr">
+        <is>
+          <t>GT7108</t>
+        </is>
+      </c>
+      <c r="C280" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D280" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E280" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F280" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G280" s="86" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="H280" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I280" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J280" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K280" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2816 Ad Plastik</t>
+        </is>
+      </c>
+      <c r="L280" s="33" t="inlineStr">
+        <is>
+          <t>[Gina]</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B281" s="29" t="inlineStr">
+        <is>
+          <t>NITTO SPV9310</t>
+        </is>
+      </c>
+      <c r="C281" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D281" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E281" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F281" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G281" s="86" t="n">
+        <v>1.327</v>
+      </c>
+      <c r="H281" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I281" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J281" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K281" s="32" t="inlineStr">
+        <is>
+          <t>PRET 93010</t>
+        </is>
+      </c>
+      <c r="L281" s="33" t="inlineStr">
+        <is>
+          <t>[Gina]</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B282" s="29" t="inlineStr">
+        <is>
+          <t>D41170 GRA</t>
+        </is>
+      </c>
+      <c r="C282" s="28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D282" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E282" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F282" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G282" s="86" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H282" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I282" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J282" s="31" t="inlineStr">
+        <is>
+          <t>Neveon</t>
+        </is>
+      </c>
+      <c r="K282" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2818</t>
+        </is>
+      </c>
+      <c r="L282" s="33" t="inlineStr">
+        <is>
+          <t>[Gina]; 2000×1000×20mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B283" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TESA 50118-00008-01</t>
+        </is>
+      </c>
+      <c r="C283" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="D283" s="28" t="n">
+        <v>75</v>
+      </c>
+      <c r="E283" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F283" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G283" s="86" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="H283" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I283" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J283" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K283" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2818</t>
+        </is>
+      </c>
+      <c r="L283" s="33" t="inlineStr">
+        <is>
+          <t>[Gina]; 3.75mp/rolă</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B284" s="29" t="inlineStr">
+        <is>
+          <t>Role EPDM-W 8mm</t>
+        </is>
+      </c>
+      <c r="C284" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D284" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E284" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F284" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G284" s="86" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H284" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I284" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J284" s="31" t="inlineStr"/>
+      <c r="K284" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2819</t>
+        </is>
+      </c>
+      <c r="L284" s="33" t="inlineStr">
+        <is>
+          <t>[Gina]; 20m×1000×8mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B285" s="29" t="inlineStr">
+        <is>
+          <t>Nitto 5015T</t>
+        </is>
+      </c>
+      <c r="C285" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D285" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E285" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F285" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G285" s="86" t="n">
+        <v>5</v>
+      </c>
+      <c r="H285" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I285" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J285" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K285" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2819</t>
+        </is>
+      </c>
+      <c r="L285" s="33" t="inlineStr">
+        <is>
+          <t>[Gina]</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B286" s="29" t="inlineStr">
+        <is>
+          <t>BANDA S4610MF ATP</t>
+        </is>
+      </c>
+      <c r="C286" s="28" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D286" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E286" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F286" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G286" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="H286" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I286" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J286" s="31" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="K286" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2819</t>
+        </is>
+      </c>
+      <c r="L286" s="33" t="inlineStr">
+        <is>
+          <t>[Gina]</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B287" s="29" t="inlineStr">
+        <is>
+          <t>BANDA S4707MF ATP</t>
+        </is>
+      </c>
+      <c r="C287" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D287" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="E287" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F287" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G287" s="86" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H287" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I287" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J287" s="31" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="K287" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2819</t>
+        </is>
+      </c>
+      <c r="L287" s="33" t="inlineStr">
+        <is>
+          <t>[Gina]</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B288" s="29" t="inlineStr">
+        <is>
+          <t>Toray Airlite 230 22mm</t>
+        </is>
+      </c>
+      <c r="C288" s="28" t="n">
+        <v>925</v>
+      </c>
+      <c r="D288" s="28" t="n">
+        <v>120</v>
+      </c>
+      <c r="E288" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="F288" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G288" s="86" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H288" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I288" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J288" s="31" t="inlineStr">
+        <is>
+          <t>Toray</t>
+        </is>
+      </c>
+      <c r="K288" s="32" t="inlineStr">
+        <is>
+          <t>Airlite Izolatiq</t>
+        </is>
+      </c>
+      <c r="L288" s="33" t="inlineStr">
+        <is>
+          <t>acustic</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B289" s="29" t="inlineStr">
+        <is>
+          <t>Toray Airlite 350 26mm</t>
+        </is>
+      </c>
+      <c r="C289" s="28" t="n">
+        <v>925</v>
+      </c>
+      <c r="D289" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="E289" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="F289" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G289" s="86" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H289" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I289" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J289" s="31" t="inlineStr">
+        <is>
+          <t>Toray</t>
+        </is>
+      </c>
+      <c r="K289" s="32" t="inlineStr">
+        <is>
+          <t>Airlite Izolatiq</t>
+        </is>
+      </c>
+      <c r="L289" s="33" t="inlineStr">
+        <is>
+          <t>acustic</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B290" s="29" t="inlineStr">
+        <is>
+          <t>3M TF1500 ACST 43785</t>
+        </is>
+      </c>
+      <c r="C290" s="28" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D290" s="28" t="n">
+        <v>190</v>
+      </c>
+      <c r="E290" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F290" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G290" s="86" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H290" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I290" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J290" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K290" s="32" t="inlineStr">
+        <is>
+          <t>Meta_1510 XEV</t>
+        </is>
+      </c>
+      <c r="L290" s="33" t="inlineStr">
+        <is>
+          <t>[Andrei]; pricing 2023 RO; 427.46€/rolă</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B291" s="29" t="inlineStr">
+        <is>
+          <t>BANDA S-4610MF ATP</t>
+        </is>
+      </c>
+      <c r="C291" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D291" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E291" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F291" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G291" s="86" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H291" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I291" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J291" s="31" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="K291" s="32" t="inlineStr">
+        <is>
+          <t>Meta_1510 XEV</t>
+        </is>
+      </c>
+      <c r="L291" s="33" t="inlineStr">
+        <is>
+          <t>[Andrei]; adeziv</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B292" s="29" t="inlineStr">
+        <is>
+          <t>Role Koepp EPDM-1000 20mm</t>
+        </is>
+      </c>
+      <c r="C292" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D292" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E292" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F292" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G292" s="86" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="H292" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I292" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J292" s="31" t="inlineStr">
+        <is>
+          <t>Koepp</t>
+        </is>
+      </c>
+      <c r="K292" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2690 AD Plastik</t>
+        </is>
+      </c>
+      <c r="L292" s="33" t="inlineStr">
+        <is>
+          <t>[Gina]; EXW; 20m×1000×20mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B293" s="29" t="inlineStr">
+        <is>
+          <t>3M™ VHB™ Tape 4914 White 0.25mm</t>
+        </is>
+      </c>
+      <c r="C293" s="28" t="n">
+        <v>600</v>
+      </c>
+      <c r="D293" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E293" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F293" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G293" s="86" t="n">
+        <v>38</v>
+      </c>
+      <c r="H293" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I293" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J293" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K293" s="32" t="inlineStr">
+        <is>
+          <t>3M Converter / PRJM 2824</t>
+        </is>
+      </c>
+      <c r="L293" s="33" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B294" s="29" t="inlineStr">
+        <is>
+          <t>EPDM-S 175KG/MC 2MM BLACK</t>
+        </is>
+      </c>
+      <c r="C294" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D294" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E294" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F294" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G294" s="86" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H294" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I294" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J294" s="31" t="inlineStr"/>
+      <c r="K294" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2816 Ad Plastik</t>
+        </is>
+      </c>
+      <c r="L294" s="33" t="inlineStr">
+        <is>
+          <t>1000×20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B295" s="29" t="inlineStr">
+        <is>
+          <t>EPDM 75-0 10mm</t>
+        </is>
+      </c>
+      <c r="C295" s="28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D295" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E295" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F295" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G295" s="86" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="H295" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I295" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J295" s="31" t="inlineStr"/>
+      <c r="K295" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2816 Ad Plastik</t>
+        </is>
+      </c>
+      <c r="L295" s="33" t="inlineStr">
+        <is>
+          <t>2000×1000×10mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B296" s="29" t="inlineStr">
+        <is>
+          <t>PORON 4701-37-19020-04 0.5mm</t>
+        </is>
+      </c>
+      <c r="C296" s="28" t="n">
+        <v>1372</v>
+      </c>
+      <c r="D296" s="28" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="E296" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F296" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G296" s="86" t="n">
+        <v>30</v>
+      </c>
+      <c r="H296" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I296" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J296" s="31" t="inlineStr">
+        <is>
+          <t>Rogers</t>
+        </is>
+      </c>
+      <c r="K296" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2821 Ad Plastik</t>
+        </is>
+      </c>
+      <c r="L296" s="33" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B297" s="29" t="inlineStr">
+        <is>
+          <t>BANDA S4707MF ATP</t>
+        </is>
+      </c>
+      <c r="C297" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D297" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="E297" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F297" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G297" s="86" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H297" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I297" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J297" s="31" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="K297" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2823 cercuri felt</t>
+        </is>
+      </c>
+      <c r="L297" s="33" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B298" s="29" t="inlineStr">
+        <is>
+          <t>FOLIE R0708</t>
+        </is>
+      </c>
+      <c r="C298" s="28" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D298" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="E298" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F298" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G298" s="86" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H298" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I298" s="28" t="inlineStr">
+        <is>
+          <t>6 role</t>
+        </is>
+      </c>
+      <c r="J298" s="31" t="inlineStr"/>
+      <c r="K298" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2822 Mondo Style</t>
+        </is>
+      </c>
+      <c r="L298" s="33" t="inlineStr">
+        <is>
+          <t>390€/rolă</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B299" s="29" t="inlineStr">
+        <is>
+          <t>FOLIE R0301</t>
+        </is>
+      </c>
+      <c r="C299" s="28" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D299" s="28" t="n">
+        <v>350</v>
+      </c>
+      <c r="E299" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F299" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G299" s="86" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H299" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I299" s="28" t="inlineStr">
+        <is>
+          <t>6 role</t>
+        </is>
+      </c>
+      <c r="J299" s="31" t="inlineStr"/>
+      <c r="K299" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2822 Mondo Style</t>
+        </is>
+      </c>
+      <c r="L299" s="33" t="inlineStr">
+        <is>
+          <t>161.54€/rolă</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B300" s="29" t="inlineStr">
+        <is>
+          <t>3M™ VHB™ Tape 5925F Black 0.6mm</t>
+        </is>
+      </c>
+      <c r="C300" s="28" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D300" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E300" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F300" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G300" s="86" t="n">
+        <v>65</v>
+      </c>
+      <c r="H300" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I300" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J300" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K300" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2825 Drakuplast</t>
+        </is>
+      </c>
+      <c r="L300" s="33" t="inlineStr">
+        <is>
+          <t>pret nou 3M (de la 86.50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B301" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Acrylic Foam Tape GT6006P Gray 0.6mm</t>
+        </is>
+      </c>
+      <c r="C301" s="28" t="n">
+        <v>609</v>
+      </c>
+      <c r="D301" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E301" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F301" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G301" s="86" t="n">
+        <v>13</v>
+      </c>
+      <c r="H301" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I301" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J301" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K301" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2825 Drakuplast</t>
+        </is>
+      </c>
+      <c r="L301" s="33" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B302" s="29" t="inlineStr">
+        <is>
+          <t>3M™ VHB™ Tape GPH-060GF Grey</t>
+        </is>
+      </c>
+      <c r="C302" s="28" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D302" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E302" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F302" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G302" s="86" t="n">
+        <v>28</v>
+      </c>
+      <c r="H302" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I302" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J302" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K302" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2825 Drakuplast</t>
+        </is>
+      </c>
+      <c r="L302" s="33" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B303" s="29" t="inlineStr">
+        <is>
+          <t>Koepp K/PE 35 W 10mm</t>
+        </is>
+      </c>
+      <c r="C303" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D303" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E303" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F303" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G303" s="86" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="H303" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I303" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J303" s="31" t="inlineStr">
+        <is>
+          <t>Koepp</t>
+        </is>
+      </c>
+      <c r="K303" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2827</t>
+        </is>
+      </c>
+      <c r="L303" s="33" t="inlineStr">
+        <is>
+          <t>1200×1000×10mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B304" s="29" t="inlineStr">
+        <is>
+          <t>EPDM-S 8mm</t>
+        </is>
+      </c>
+      <c r="C304" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D304" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E304" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F304" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G304" s="86" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="H304" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I304" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J304" s="31" t="inlineStr"/>
+      <c r="K304" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2810 Ford Geely</t>
+        </is>
+      </c>
+      <c r="L304" s="33" t="inlineStr">
+        <is>
+          <t>20m×1000×8mm; idem 15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B305" s="29" t="inlineStr">
+        <is>
+          <t>PU FOAM D30130X 20mm</t>
+        </is>
+      </c>
+      <c r="C305" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D305" s="28" t="n">
+        <v>57</v>
+      </c>
+      <c r="E305" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F305" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G305" s="86" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="H305" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I305" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J305" s="31" t="inlineStr">
+        <is>
+          <t>Neveon</t>
+        </is>
+      </c>
+      <c r="K305" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2690 AD Plastik</t>
+        </is>
+      </c>
+      <c r="L305" s="33" t="inlineStr">
+        <is>
+          <t>update de la 6.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B306" s="29" t="inlineStr">
+        <is>
+          <t>Armacell EF090 20mm</t>
+        </is>
+      </c>
+      <c r="C306" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D306" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="E306" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F306" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G306" s="86" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="H306" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I306" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J306" s="31" t="inlineStr">
+        <is>
+          <t>Armacell</t>
+        </is>
+      </c>
+      <c r="K306" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2690 AD Plastik</t>
+        </is>
+      </c>
+      <c r="L306" s="33" t="inlineStr">
+        <is>
+          <t>2 skin</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B307" s="29" t="inlineStr">
+        <is>
+          <t>NITTO SPV4088RF TRANSPARENT</t>
+        </is>
+      </c>
+      <c r="C307" s="28" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D307" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="E307" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F307" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G307" s="86" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H307" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I307" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J307" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K307" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2834 Plastor</t>
+        </is>
+      </c>
+      <c r="L307" s="33" t="inlineStr">
+        <is>
+          <t>folie protectie</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B308" s="29" t="inlineStr">
+        <is>
+          <t>Nitto EE1010 5mm</t>
+        </is>
+      </c>
+      <c r="C308" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D308" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="E308" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F308" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G308" s="86" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H308" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I308" s="28" t="inlineStr">
+        <is>
+          <t>4 role</t>
+        </is>
+      </c>
+      <c r="J308" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K308" s="32" t="inlineStr">
+        <is>
+          <t>PRJM 2832 Delta Nord</t>
+        </is>
+      </c>
+      <c r="L308" s="33" t="inlineStr">
+        <is>
+          <t>DDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B309" s="29" t="inlineStr">
+        <is>
+          <t>Nitto EE1010 8mm</t>
+        </is>
+      </c>
+      <c r="C309" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D309" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="E309" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F309" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G309" s="86" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H309" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I309" s="28" t="inlineStr">
+        <is>
+          <t>4 role</t>
+        </is>
+      </c>
+      <c r="J309" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K309" s="32" t="inlineStr">
+        <is>
+          <t>PRJM 2832 Delta Nord</t>
+        </is>
+      </c>
+      <c r="L309" s="33" t="inlineStr">
+        <is>
+          <t>DDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B310" s="29" t="inlineStr">
+        <is>
+          <t>NITTO SPV4057R</t>
+        </is>
+      </c>
+      <c r="C310" s="28" t="n">
+        <v>1560</v>
+      </c>
+      <c r="D310" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="E310" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F310" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G310" s="86" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H310" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I310" s="28" t="inlineStr">
+        <is>
+          <t>5 logrole</t>
+        </is>
+      </c>
+      <c r="J310" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K310" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2834 Plastor</t>
+        </is>
+      </c>
+      <c r="L310" s="33" t="inlineStr">
+        <is>
+          <t>DDP; untrimmed logroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B311" s="29" t="inlineStr">
+        <is>
+          <t>Rogers HT840</t>
+        </is>
+      </c>
+      <c r="C311" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D311" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E311" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F311" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G311" s="86" t="n">
+        <v>2234</v>
+      </c>
+      <c r="H311" s="28" t="inlineStr">
+        <is>
+          <t>€/rolă</t>
+        </is>
+      </c>
+      <c r="I311" s="28" t="inlineStr">
+        <is>
+          <t>1 rolă</t>
+        </is>
+      </c>
+      <c r="J311" s="31" t="inlineStr">
+        <is>
+          <t>Rogers</t>
+        </is>
+      </c>
+      <c r="K311" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2789 Joysonquin</t>
+        </is>
+      </c>
+      <c r="L311" s="33" t="inlineStr">
+        <is>
+          <t>16-18 sapt</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B312" s="29" t="inlineStr">
+        <is>
+          <t>Koepp K/PE 45 W 10mm</t>
+        </is>
+      </c>
+      <c r="C312" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D312" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E312" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F312" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G312" s="86" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="H312" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I312" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J312" s="31" t="inlineStr">
+        <is>
+          <t>Koepp</t>
+        </is>
+      </c>
+      <c r="K312" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2827</t>
+        </is>
+      </c>
+      <c r="L312" s="33" t="inlineStr">
+        <is>
+          <t>densitate 45kg; 1200×1000×10mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B313" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Acrylic Foam Tape PX5011F Gray 1.14mm</t>
+        </is>
+      </c>
+      <c r="C313" s="28" t="n">
+        <v>1230</v>
+      </c>
+      <c r="D313" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E313" s="28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F313" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G313" s="86" t="n">
+        <v>47</v>
+      </c>
+      <c r="H313" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I313" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J313" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K313" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2840 Ad Plastik</t>
+        </is>
+      </c>
+      <c r="L313" s="33" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B314" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Acrylic Foam Tape PX5008F Gray 0.8mm</t>
+        </is>
+      </c>
+      <c r="C314" s="28" t="n">
+        <v>1230</v>
+      </c>
+      <c r="D314" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E314" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F314" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G314" s="86" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="H314" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I314" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J314" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K314" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2840 Ad Plastik</t>
+        </is>
+      </c>
+      <c r="L314" s="33" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B315" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Acrylic Foam Tape PX5011F Gray 1.14mm</t>
+        </is>
+      </c>
+      <c r="C315" s="28" t="n">
+        <v>1230</v>
+      </c>
+      <c r="D315" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E315" s="28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F315" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G315" s="86" t="n">
+        <v>46.58</v>
+      </c>
+      <c r="H315" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I315" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J315" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K315" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2833 Ad Plastik</t>
+        </is>
+      </c>
+      <c r="L315" s="33" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B316" s="29" t="inlineStr">
+        <is>
+          <t>BANDA DUPLOCOLL 5016F</t>
+        </is>
+      </c>
+      <c r="C316" s="28" t="n">
+        <v>1260</v>
+      </c>
+      <c r="D316" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E316" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F316" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G316" s="86" t="n">
+        <v>13</v>
+      </c>
+      <c r="H316" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I316" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J316" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K316" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2845 Delonghi</t>
+        </is>
+      </c>
+      <c r="L316" s="33" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B317" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Acrylic Plus Tape EX4011 Black 1.1mm</t>
+        </is>
+      </c>
+      <c r="C317" s="28" t="n">
+        <v>1220</v>
+      </c>
+      <c r="D317" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E317" s="28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F317" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G317" s="86" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="H317" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I317" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J317" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K317" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2841 Optimatrix</t>
+        </is>
+      </c>
+      <c r="L317" s="33" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B318" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TESA 51136</t>
+        </is>
+      </c>
+      <c r="C318" s="28" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D318" s="28" t="n">
+        <v>330</v>
+      </c>
+      <c r="E318" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F318" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G318" s="86" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H318" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I318" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J318" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K318" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2741 Topia</t>
+        </is>
+      </c>
+      <c r="L318" s="33" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B319" s="29" t="inlineStr">
+        <is>
+          <t>Liner 1 side</t>
+        </is>
+      </c>
+      <c r="C319" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D319" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E319" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F319" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G319" s="86" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H319" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I319" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J319" s="31" t="inlineStr"/>
+      <c r="K319" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2706 ASA</t>
+        </is>
+      </c>
+      <c r="L319" s="33" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B320" s="29" t="inlineStr">
+        <is>
+          <t>EPDM SC-W 100KG/MC 5MM BLACK</t>
+        </is>
+      </c>
+      <c r="C320" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D320" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E320" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F320" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G320" s="86" t="n">
+        <v>13</v>
+      </c>
+      <c r="H320" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I320" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J320" s="31" t="inlineStr"/>
+      <c r="K320" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2059 Maroc</t>
+        </is>
+      </c>
+      <c r="L320" s="33" t="inlineStr">
+        <is>
+          <t>1000×20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B321" s="29" t="inlineStr">
+        <is>
+          <t>Nitto EE1010 5mm</t>
+        </is>
+      </c>
+      <c r="C321" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D321" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="E321" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F321" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G321" s="86" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H321" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I321" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J321" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K321" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2059 Maroc</t>
+        </is>
+      </c>
+      <c r="L321" s="33" t="inlineStr">
+        <is>
+          <t>1000×35m</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B322" s="29" t="inlineStr">
+        <is>
+          <t>Koepp K/PE 30 A 10mm</t>
+        </is>
+      </c>
+      <c r="C322" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D322" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E322" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F322" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G322" s="86" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="H322" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I322" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J322" s="31" t="inlineStr">
+        <is>
+          <t>Koepp</t>
+        </is>
+      </c>
+      <c r="K322" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2403</t>
+        </is>
+      </c>
+      <c r="L322" s="33" t="inlineStr">
+        <is>
+          <t>20m×1200×10mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B323" s="29" t="inlineStr">
+        <is>
+          <t>Nomex 410</t>
+        </is>
+      </c>
+      <c r="C323" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="D323" s="28" t="n">
+        <v>439</v>
+      </c>
+      <c r="E323" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F323" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G323" s="86" t="n">
+        <v>38</v>
+      </c>
+      <c r="H323" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I323" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J323" s="31" t="inlineStr"/>
+      <c r="K323" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2843 Polycontact</t>
+        </is>
+      </c>
+      <c r="L323" s="33" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B324" s="29" t="inlineStr">
+        <is>
+          <t>BANDA S-4111 FL/B</t>
+        </is>
+      </c>
+      <c r="C324" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D324" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="E324" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F324" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G324" s="86" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H324" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I324" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J324" s="31" t="inlineStr">
+        <is>
+          <t>Neveon</t>
+        </is>
+      </c>
+      <c r="K324" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2843 Polycontact</t>
+        </is>
+      </c>
+      <c r="L324" s="33" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B325" s="29" t="inlineStr">
+        <is>
+          <t>PPF320GF+</t>
+        </is>
+      </c>
+      <c r="C325" s="28" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D325" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E325" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F325" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G325" s="86" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="H325" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I325" s="28" t="inlineStr">
+        <is>
+          <t>10 buc</t>
+        </is>
+      </c>
+      <c r="J325" s="31" t="inlineStr"/>
+      <c r="K325" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2838</t>
+        </is>
+      </c>
+      <c r="L325" s="33" t="inlineStr">
+        <is>
+          <t>alt. la 3M PU5020P; 4-6 sapt</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B326" s="29" t="inlineStr">
+        <is>
+          <t>BANDA FLEECE FT 0900X</t>
+        </is>
+      </c>
+      <c r="C326" s="28" t="n">
+        <v>1371</v>
+      </c>
+      <c r="D326" s="28" t="n">
+        <v>73</v>
+      </c>
+      <c r="E326" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F326" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G326" s="86" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="H326" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I326" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J326" s="31" t="inlineStr"/>
+      <c r="K326" s="32" t="inlineStr">
+        <is>
+          <t>Adhesive flock tape</t>
+        </is>
+      </c>
+      <c r="L326" s="33" t="inlineStr">
+        <is>
+          <t>PP compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B327" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TESA 60307</t>
+        </is>
+      </c>
+      <c r="C327" s="28" t="n">
+        <v>1140</v>
+      </c>
+      <c r="D327" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="E327" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F327" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G327" s="86" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="H327" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I327" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J327" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K327" s="32" t="inlineStr">
+        <is>
+          <t>Adhesive flock tape</t>
+        </is>
+      </c>
+      <c r="L327" s="33" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B328" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TESA 60310 Black PET Fleece</t>
+        </is>
+      </c>
+      <c r="C328" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D328" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E328" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F328" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G328" s="86" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H328" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I328" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J328" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K328" s="32" t="inlineStr">
+        <is>
+          <t>Adhesive flock tape</t>
+        </is>
+      </c>
+      <c r="L328" s="33" t="inlineStr">
+        <is>
+          <t>525µm</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B329" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TESA 04688-00046-01 RED</t>
+        </is>
+      </c>
+      <c r="C329" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="D329" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="E329" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F329" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G329" s="86" t="n">
+        <v>5</v>
+      </c>
+      <c r="H329" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I329" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J329" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K329" s="32" t="inlineStr">
+        <is>
+          <t>Cerere pret</t>
+        </is>
+      </c>
+      <c r="L329" s="33" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B330" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TESA 04688-50001-00 Silver</t>
+        </is>
+      </c>
+      <c r="C330" s="28" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D330" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E330" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F330" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G330" s="86" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H330" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I330" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J330" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K330" s="32" t="inlineStr">
+        <is>
+          <t>Cerere pret</t>
+        </is>
+      </c>
+      <c r="L330" s="33" t="inlineStr">
+        <is>
+          <t>articol stoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B331" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Dual Lock DL250H/PX5011 32531</t>
+        </is>
+      </c>
+      <c r="C331" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D331" s="28" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="E331" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F331" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G331" s="86" t="n">
+        <v>184.75</v>
+      </c>
+      <c r="H331" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I331" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J331" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K331" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2840 Ad Plastik</t>
+        </is>
+      </c>
+      <c r="L331" s="33" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B332" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Die-Cuttable Tape DC2008S2 A+</t>
+        </is>
+      </c>
+      <c r="C332" s="28" t="n">
+        <v>1193.8</v>
+      </c>
+      <c r="D332" s="28" t="n">
+        <v>132</v>
+      </c>
+      <c r="E332" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F332" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G332" s="86" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="H332" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I332" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J332" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K332" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2847 Hutchinson</t>
+        </is>
+      </c>
+      <c r="L332" s="33" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B333" s="29" t="inlineStr">
+        <is>
+          <t>RT8008 AFT</t>
+        </is>
+      </c>
+      <c r="C333" s="28" t="n">
+        <v>600</v>
+      </c>
+      <c r="D333" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E333" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F333" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G333" s="86" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="H333" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I333" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J333" s="31" t="inlineStr"/>
+      <c r="K333" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2849 Ad Plastik</t>
+        </is>
+      </c>
+      <c r="L333" s="33" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B334" s="29" t="inlineStr">
+        <is>
+          <t>RT8010 AFT</t>
+        </is>
+      </c>
+      <c r="C334" s="28" t="n">
+        <v>300</v>
+      </c>
+      <c r="D334" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E334" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F334" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G334" s="86" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="H334" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I334" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J334" s="31" t="inlineStr"/>
+      <c r="K334" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2849 Ad Plastik</t>
+        </is>
+      </c>
+      <c r="L334" s="33" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B335" s="29" t="inlineStr">
+        <is>
+          <t>EPDM 130 kg/m³ 3mm</t>
+        </is>
+      </c>
+      <c r="C335" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D335" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E335" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F335" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G335" s="86" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H335" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I335" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J335" s="31" t="inlineStr"/>
+      <c r="K335" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2852 Bandatech</t>
+        </is>
+      </c>
+      <c r="L335" s="33" t="inlineStr">
+        <is>
+          <t>DAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B336" s="29" t="inlineStr">
+        <is>
+          <t>EPDM 130 kg/m³ 6mm</t>
+        </is>
+      </c>
+      <c r="C336" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D336" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E336" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F336" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G336" s="86" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H336" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I336" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J336" s="31" t="inlineStr"/>
+      <c r="K336" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2852 Bandatech</t>
+        </is>
+      </c>
+      <c r="L336" s="33" t="inlineStr">
+        <is>
+          <t>DAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B337" s="29" t="inlineStr">
+        <is>
+          <t>Koepp K/PE30 3mm</t>
+        </is>
+      </c>
+      <c r="C337" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D337" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E337" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F337" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G337" s="86" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H337" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I337" s="28" t="inlineStr">
+        <is>
+          <t>100000 buc</t>
+        </is>
+      </c>
+      <c r="J337" s="31" t="inlineStr">
+        <is>
+          <t>Koepp</t>
+        </is>
+      </c>
+      <c r="K337" s="32" t="inlineStr">
+        <is>
+          <t>foam stickers</t>
+        </is>
+      </c>
+      <c r="L337" s="33" t="inlineStr">
+        <is>
+          <t>FCA; scapare stoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B338" s="29" t="inlineStr">
+        <is>
+          <t>Saint-Gobain 2525P2B 15mm</t>
+        </is>
+      </c>
+      <c r="C338" s="28" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D338" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E338" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="F338" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G338" s="86" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="H338" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I338" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J338" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K338" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2786</t>
+        </is>
+      </c>
+      <c r="L338" s="33" t="inlineStr">
+        <is>
+          <t>139.54€/item; investigatie DBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B339" s="29" t="inlineStr">
+        <is>
+          <t>Role EPDM-SUW 15mm</t>
+        </is>
+      </c>
+      <c r="C339" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D339" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E339" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="F339" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G339" s="86" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H339" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I339" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J339" s="31" t="inlineStr"/>
+      <c r="K339" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2786</t>
+        </is>
+      </c>
+      <c r="L339" s="33" t="inlineStr">
+        <is>
+          <t>20m×1000×15mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B340" s="29" t="inlineStr">
+        <is>
+          <t>Saint-Gobain P335</t>
+        </is>
+      </c>
+      <c r="C340" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D340" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E340" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F340" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G340" s="86" t="n">
+        <v>5</v>
+      </c>
+      <c r="H340" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I340" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J340" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K340" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2868</t>
+        </is>
+      </c>
+      <c r="L340" s="33" t="inlineStr">
+        <is>
+          <t>pret achizitie estimat</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B341" s="29" t="inlineStr">
+        <is>
+          <t>Saint-Gobain TRP5300</t>
+        </is>
+      </c>
+      <c r="C341" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D341" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E341" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F341" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G341" s="86" t="n">
+        <v>15</v>
+      </c>
+      <c r="H341" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I341" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J341" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K341" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2868</t>
+        </is>
+      </c>
+      <c r="L341" s="33" t="inlineStr">
+        <is>
+          <t>pret estimat</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B342" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Acrylic Foam Tape GT6006P Gray 0.6mm</t>
+        </is>
+      </c>
+      <c r="C342" s="28" t="n">
+        <v>609</v>
+      </c>
+      <c r="D342" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E342" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F342" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G342" s="86" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H342" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I342" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J342" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K342" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2869 Visteon</t>
+        </is>
+      </c>
+      <c r="L342" s="33" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B343" s="29" t="inlineStr">
+        <is>
+          <t>Koepp K/PE 30 ANTRACIT 3mm</t>
+        </is>
+      </c>
+      <c r="C343" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D343" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E343" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F343" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G343" s="86" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H343" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I343" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J343" s="31" t="inlineStr">
+        <is>
+          <t>Koepp</t>
+        </is>
+      </c>
+      <c r="K343" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2870 Emerson</t>
+        </is>
+      </c>
+      <c r="L343" s="33" t="inlineStr">
+        <is>
+          <t>20m×1200×3mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B344" s="29" t="inlineStr">
+        <is>
+          <t>PET FILM SP6T2/PAS Silicone 0.06mm</t>
+        </is>
+      </c>
+      <c r="C344" s="28" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D344" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="E344" s="28" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F344" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G344" s="86" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H344" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I344" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J344" s="31" t="inlineStr"/>
+      <c r="K344" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2873 Visteon</t>
+        </is>
+      </c>
+      <c r="L344" s="33" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B345" s="29" t="inlineStr">
+        <is>
+          <t>3M™ PPF 5020P 30538</t>
+        </is>
+      </c>
+      <c r="C345" s="28" t="n">
+        <v>610</v>
+      </c>
+      <c r="D345" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E345" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F345" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G345" s="86" t="n">
+        <v>71</v>
+      </c>
+      <c r="H345" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I345" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J345" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K345" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2863</t>
+        </is>
+      </c>
+      <c r="L345" s="33" t="inlineStr">
+        <is>
+          <t>folie protectie pietre</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B346" s="29" t="inlineStr">
+        <is>
+          <t>tesa® 52995 PV4</t>
+        </is>
+      </c>
+      <c r="C346" s="28" t="n">
+        <v>1245</v>
+      </c>
+      <c r="D346" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E346" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F346" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G346" s="86" t="n">
+        <v>66</v>
+      </c>
+      <c r="H346" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I346" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J346" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K346" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2863</t>
+        </is>
+      </c>
+      <c r="L346" s="33" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B347" s="29" t="inlineStr">
+        <is>
+          <t>3M™ F-506 negru</t>
+        </is>
+      </c>
+      <c r="C347" s="28" t="n">
+        <v>1220</v>
+      </c>
+      <c r="D347" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="E347" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F347" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G347" s="86" t="n">
+        <v>17</v>
+      </c>
+      <c r="H347" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I347" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J347" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K347" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2863</t>
+        </is>
+      </c>
+      <c r="L347" s="33" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B348" s="29" t="inlineStr">
+        <is>
+          <t>ORACAL 751 negru</t>
+        </is>
+      </c>
+      <c r="C348" s="28" t="n">
+        <v>1260</v>
+      </c>
+      <c r="D348" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E348" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F348" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G348" s="86" t="n">
+        <v>9</v>
+      </c>
+      <c r="H348" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I348" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J348" s="31" t="inlineStr">
+        <is>
+          <t>Orafol</t>
+        </is>
+      </c>
+      <c r="K348" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2863</t>
+        </is>
+      </c>
+      <c r="L348" s="33" t="inlineStr">
+        <is>
+          <t>+TVA; dunga neagra</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B349" s="29" t="inlineStr">
+        <is>
+          <t>EPDM 79-2 2mm</t>
+        </is>
+      </c>
+      <c r="C349" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D349" s="28" t="n">
+        <v>84</v>
+      </c>
+      <c r="E349" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F349" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G349" s="86" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H349" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I349" s="28" t="inlineStr">
+        <is>
+          <t>8 role</t>
+        </is>
+      </c>
+      <c r="J349" s="31" t="inlineStr"/>
+      <c r="K349" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2838</t>
+        </is>
+      </c>
+      <c r="L349" s="33" t="inlineStr">
+        <is>
+          <t>1000×84m</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B350" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Copper Foil Shielding Tape 1181 MC19 12mm</t>
+        </is>
+      </c>
+      <c r="C350" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="D350" s="28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E350" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F350" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G350" s="86" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="H350" s="28" t="inlineStr">
+        <is>
+          <t>€/buc</t>
+        </is>
+      </c>
+      <c r="I350" s="28" t="inlineStr">
+        <is>
+          <t>19 buc</t>
+        </is>
+      </c>
+      <c r="J350" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K350" s="32" t="inlineStr">
+        <is>
+          <t>Cda banda cupru</t>
+        </is>
+      </c>
+      <c r="L350" s="33" t="inlineStr">
+        <is>
+          <t>6-8 sapt</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B351" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Copper Foil Shielding Tape 1181 MC19 25mm</t>
+        </is>
+      </c>
+      <c r="C351" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D351" s="28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E351" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F351" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G351" s="86" t="n">
+        <v>72.79000000000001</v>
+      </c>
+      <c r="H351" s="28" t="inlineStr">
+        <is>
+          <t>€/buc</t>
+        </is>
+      </c>
+      <c r="I351" s="28" t="inlineStr">
+        <is>
+          <t>9 buc</t>
+        </is>
+      </c>
+      <c r="J351" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K351" s="32" t="inlineStr">
+        <is>
+          <t>Cda banda cupru</t>
+        </is>
+      </c>
+      <c r="L351" s="33" t="inlineStr">
+        <is>
+          <t>3-4 sapt</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B352" s="29" t="inlineStr">
+        <is>
+          <t>Norseal 2521 3mm</t>
+        </is>
+      </c>
+      <c r="C352" s="28" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D352" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E352" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F352" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G352" s="86" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="H352" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I352" s="28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J352" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K352" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2767 Amusnet</t>
+        </is>
+      </c>
+      <c r="L352" s="33" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B353" s="29" t="inlineStr">
+        <is>
+          <t>Norseal 4031 1.5mm</t>
+        </is>
+      </c>
+      <c r="C353" s="28" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D353" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="E353" s="28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F353" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G353" s="86" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H353" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I353" s="28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J353" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K353" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2767 Amusnet</t>
+        </is>
+      </c>
+      <c r="L353" s="33" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B354" s="29" t="inlineStr">
+        <is>
+          <t>Norseal 4031 3mm</t>
+        </is>
+      </c>
+      <c r="C354" s="28" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D354" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E354" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F354" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G354" s="86" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="H354" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I354" s="28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J354" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K354" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2767 Amusnet</t>
+        </is>
+      </c>
+      <c r="L354" s="33" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B355" s="29" t="inlineStr">
+        <is>
+          <t>Norseal 5041 1.5mm</t>
+        </is>
+      </c>
+      <c r="C355" s="28" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D355" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="E355" s="28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F355" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G355" s="86" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="H355" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I355" s="28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J355" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K355" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2767 Amusnet</t>
+        </is>
+      </c>
+      <c r="L355" s="33" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B356" s="29" t="inlineStr">
+        <is>
+          <t>Norseal 5041 3mm</t>
+        </is>
+      </c>
+      <c r="C356" s="28" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D356" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E356" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F356" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G356" s="86" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="H356" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I356" s="28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J356" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K356" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2767 Amusnet</t>
+        </is>
+      </c>
+      <c r="L356" s="33" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B357" s="29" t="inlineStr">
+        <is>
+          <t>Norbond A7300 1.1mm</t>
+        </is>
+      </c>
+      <c r="C357" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D357" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E357" s="28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F357" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G357" s="86" t="n">
+        <v>30.72</v>
+      </c>
+      <c r="H357" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I357" s="28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J357" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K357" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2767 Amusnet</t>
+        </is>
+      </c>
+      <c r="L357" s="33" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B358" s="29" t="inlineStr">
+        <is>
+          <t>Norbond A7300 0.8mm</t>
+        </is>
+      </c>
+      <c r="C358" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D358" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E358" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F358" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G358" s="86" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="H358" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I358" s="28" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J358" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K358" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2767 Amusnet</t>
+        </is>
+      </c>
+      <c r="L358" s="33" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B359" s="29" t="inlineStr">
+        <is>
+          <t>Norbond A7500 1.1mm</t>
+        </is>
+      </c>
+      <c r="C359" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D359" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E359" s="28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F359" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G359" s="86" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="H359" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I359" s="28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J359" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K359" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2767 Amusnet</t>
+        </is>
+      </c>
+      <c r="L359" s="33" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B360" s="29" t="inlineStr">
+        <is>
+          <t>Norbond A7500 0.7mm</t>
+        </is>
+      </c>
+      <c r="C360" s="28" t="n">
+        <v>800</v>
+      </c>
+      <c r="D360" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E360" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F360" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G360" s="86" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="H360" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I360" s="28" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J360" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K360" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2767 Amusnet</t>
+        </is>
+      </c>
+      <c r="L360" s="33" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B361" s="29" t="inlineStr">
+        <is>
+          <t>Koepp K/PE 40 CN 10mm</t>
+        </is>
+      </c>
+      <c r="C361" s="28" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D361" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E361" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F361" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G361" s="86" t="n">
+        <v>16</v>
+      </c>
+      <c r="H361" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I361" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J361" s="31" t="inlineStr">
+        <is>
+          <t>Koepp</t>
+        </is>
+      </c>
+      <c r="K361" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2861 Cellutec</t>
+        </is>
+      </c>
+      <c r="L361" s="33" t="inlineStr">
+        <is>
+          <t>2100×1200×10mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B362" s="29" t="inlineStr">
+        <is>
+          <t>Oring OR 126.67×2.62 NBR70</t>
+        </is>
+      </c>
+      <c r="C362" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D362" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E362" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F362" s="28" t="inlineStr">
+        <is>
+          <t>buc</t>
+        </is>
+      </c>
+      <c r="G362" s="86" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="H362" s="28" t="inlineStr">
+        <is>
+          <t>€/buc</t>
+        </is>
+      </c>
+      <c r="I362" s="28" t="inlineStr">
+        <is>
+          <t>6000 buc</t>
+        </is>
+      </c>
+      <c r="J362" s="31" t="inlineStr"/>
+      <c r="K362" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2876</t>
+        </is>
+      </c>
+      <c r="L362" s="33" t="inlineStr">
+        <is>
+          <t>2-3 sapt</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B363" s="29" t="inlineStr">
+        <is>
+          <t>Oring OR 126.67×2.62 EPDM70</t>
+        </is>
+      </c>
+      <c r="C363" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D363" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E363" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F363" s="28" t="inlineStr">
+        <is>
+          <t>buc</t>
+        </is>
+      </c>
+      <c r="G363" s="86" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="H363" s="28" t="inlineStr">
+        <is>
+          <t>€/buc</t>
+        </is>
+      </c>
+      <c r="I363" s="28" t="inlineStr">
+        <is>
+          <t>6000 buc</t>
+        </is>
+      </c>
+      <c r="J363" s="31" t="inlineStr"/>
+      <c r="K363" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2876</t>
+        </is>
+      </c>
+      <c r="L363" s="33" t="inlineStr">
+        <is>
+          <t>stoc 2-3 sapt / productie 25-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B364" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Adhesive Transfer Tape 468MP</t>
+        </is>
+      </c>
+      <c r="C364" s="28" t="n">
+        <v>508</v>
+      </c>
+      <c r="D364" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="E364" s="28" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F364" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G364" s="86" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="H364" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I364" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J364" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K364" s="32" t="inlineStr">
+        <is>
+          <t>Inele 7955MP</t>
+        </is>
+      </c>
+      <c r="L364" s="33" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B365" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Acrylic Plus Tape PT1500 black 1.52mm</t>
+        </is>
+      </c>
+      <c r="C365" s="28" t="n">
+        <v>1220</v>
+      </c>
+      <c r="D365" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E365" s="28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F365" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G365" s="86" t="n">
+        <v>47</v>
+      </c>
+      <c r="H365" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I365" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J365" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K365" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2838</t>
+        </is>
+      </c>
+      <c r="L365" s="33" t="inlineStr">
+        <is>
+          <t>cunoscut la Daimler</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B366" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Thinsulate™ TC1503</t>
+        </is>
+      </c>
+      <c r="C366" s="28" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D366" s="28" t="n">
+        <v>266</v>
+      </c>
+      <c r="E366" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F366" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G366" s="86" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H366" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I366" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J366" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K366" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2885</t>
+        </is>
+      </c>
+      <c r="L366" s="33" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B367" s="29" t="inlineStr">
+        <is>
+          <t>PUR D45190</t>
+        </is>
+      </c>
+      <c r="C367" s="28" t="n">
+        <v>850</v>
+      </c>
+      <c r="D367" s="28" t="n">
+        <v>560</v>
+      </c>
+      <c r="E367" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F367" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G367" s="86" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H367" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I367" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J367" s="31" t="inlineStr"/>
+      <c r="K367" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2856 Inteva</t>
+        </is>
+      </c>
+      <c r="L367" s="33" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B368" s="29" t="inlineStr">
+        <is>
+          <t>PORON 4790-92-20081-04 2.06mm</t>
+        </is>
+      </c>
+      <c r="C368" s="28" t="n">
+        <v>1372</v>
+      </c>
+      <c r="D368" s="28" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="E368" s="28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F368" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G368" s="86" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="H368" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I368" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J368" s="31" t="inlineStr">
+        <is>
+          <t>Rogers</t>
+        </is>
+      </c>
+      <c r="K368" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2856 Inteva</t>
+        </is>
+      </c>
+      <c r="L368" s="33" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B369" s="29" t="inlineStr">
+        <is>
+          <t>Koepp K/PE 65 Black 11mm</t>
+        </is>
+      </c>
+      <c r="C369" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D369" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E369" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="F369" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G369" s="86" t="n">
+        <v>11</v>
+      </c>
+      <c r="H369" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I369" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J369" s="31" t="inlineStr">
+        <is>
+          <t>Koepp</t>
+        </is>
+      </c>
+      <c r="K369" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2893 Volvo</t>
+        </is>
+      </c>
+      <c r="L369" s="33" t="inlineStr">
+        <is>
+          <t>EXW; 20m×1200×11mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B370" s="29" t="inlineStr">
+        <is>
+          <t>Koepp K/PE 70 White 7mm</t>
+        </is>
+      </c>
+      <c r="C370" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D370" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E370" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F370" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G370" s="86" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="H370" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I370" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J370" s="31" t="inlineStr">
+        <is>
+          <t>Koepp</t>
+        </is>
+      </c>
+      <c r="K370" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2893 Volvo</t>
+        </is>
+      </c>
+      <c r="L370" s="33" t="inlineStr">
+        <is>
+          <t>EXW; 20m×1200×7mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B371" s="29" t="inlineStr">
+        <is>
+          <t>Norseal® PF 27-200 1mm</t>
+        </is>
+      </c>
+      <c r="C371" s="28" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D371" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="E371" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F371" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G371" s="86" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="H371" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I371" s="28" t="inlineStr">
+        <is>
+          <t>18 buc</t>
+        </is>
+      </c>
+      <c r="J371" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K371" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2528</t>
+        </is>
+      </c>
+      <c r="L371" s="33" t="inlineStr">
+        <is>
+          <t>LT 8-10 sapt</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B372" s="29" t="inlineStr">
+        <is>
+          <t>Norseal® F20 0.8mm</t>
+        </is>
+      </c>
+      <c r="C372" s="28" t="n">
+        <v>914</v>
+      </c>
+      <c r="D372" s="28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E372" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F372" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G372" s="86" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="H372" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I372" s="28" t="inlineStr">
+        <is>
+          <t>5 buc</t>
+        </is>
+      </c>
+      <c r="J372" s="31" t="inlineStr">
+        <is>
+          <t>Saint-Gobain</t>
+        </is>
+      </c>
+      <c r="K372" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2528</t>
+        </is>
+      </c>
+      <c r="L372" s="33" t="inlineStr">
+        <is>
+          <t>LT 14-16 sapt</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B373" s="29" t="inlineStr">
+        <is>
+          <t>AFTC AM1008HC</t>
+        </is>
+      </c>
+      <c r="C373" s="28" t="n">
+        <v>900</v>
+      </c>
+      <c r="D373" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E373" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F373" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G373" s="86" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="H373" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I373" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J373" s="31" t="inlineStr">
+        <is>
+          <t>AFTC</t>
+        </is>
+      </c>
+      <c r="K373" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2884</t>
+        </is>
+      </c>
+      <c r="L373" s="33" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B374" s="29" t="inlineStr">
+        <is>
+          <t>EPDM-S 175KG/MC 1MM BLACK</t>
+        </is>
+      </c>
+      <c r="C374" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D374" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E374" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F374" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G374" s="86" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H374" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I374" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J374" s="31" t="inlineStr"/>
+      <c r="K374" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2884</t>
+        </is>
+      </c>
+      <c r="L374" s="33" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B375" s="29" t="inlineStr">
+        <is>
+          <t>Nitto No.686P 4mm</t>
+        </is>
+      </c>
+      <c r="C375" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D375" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E375" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F375" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G375" s="86" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="H375" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I375" s="28" t="inlineStr">
+        <is>
+          <t>4 role</t>
+        </is>
+      </c>
+      <c r="J375" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K375" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2884</t>
+        </is>
+      </c>
+      <c r="L375" s="33" t="inlineStr">
+        <is>
+          <t>DDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B376" s="29" t="inlineStr">
+        <is>
+          <t>BANDA TESA 50600</t>
+        </is>
+      </c>
+      <c r="C376" s="28" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D376" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E376" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F376" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G376" s="86" t="n">
+        <v>3</v>
+      </c>
+      <c r="H376" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I376" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J376" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K376" s="32" t="inlineStr">
+        <is>
+          <t>PRJM 2894 QR code</t>
+        </is>
+      </c>
+      <c r="L376" s="33" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B377" s="29" t="inlineStr">
+        <is>
+          <t>P03055B BLUE SILICONE TAPE</t>
+        </is>
+      </c>
+      <c r="C377" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="D377" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E377" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F377" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G377" s="86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H377" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I377" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J377" s="31" t="inlineStr"/>
+      <c r="K377" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2320</t>
+        </is>
+      </c>
+      <c r="L377" s="33" t="inlineStr">
+        <is>
+          <t>art.00006548</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B378" s="29" t="inlineStr">
+        <is>
+          <t>BANDA ADEZIVA GRAND GREEN</t>
+        </is>
+      </c>
+      <c r="C378" s="28" t="n">
+        <v>48</v>
+      </c>
+      <c r="D378" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E378" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F378" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G378" s="86" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H378" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I378" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J378" s="31" t="inlineStr"/>
+      <c r="K378" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2320</t>
+        </is>
+      </c>
+      <c r="L378" s="33" t="inlineStr">
+        <is>
+          <t>alb/negru/verde/albastru</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B379" s="29" t="inlineStr">
+        <is>
+          <t>FLUOROSILICONE LINER 75µm</t>
+        </is>
+      </c>
+      <c r="C379" s="28" t="n">
+        <v>520</v>
+      </c>
+      <c r="D379" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="E379" s="28" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F379" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G379" s="86" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H379" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I379" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J379" s="31" t="inlineStr"/>
+      <c r="K379" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2320</t>
+        </is>
+      </c>
+      <c r="L379" s="33" t="inlineStr">
+        <is>
+          <t>art.00006741</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B380" s="29" t="inlineStr">
+        <is>
+          <t>BANDA Tesa 50625</t>
+        </is>
+      </c>
+      <c r="C380" s="28" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D380" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E380" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F380" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G380" s="86" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H380" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I380" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J380" s="31" t="inlineStr">
+        <is>
+          <t>TESA</t>
+        </is>
+      </c>
+      <c r="K380" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2320</t>
+        </is>
+      </c>
+      <c r="L380" s="33" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B381" s="29" t="inlineStr">
+        <is>
+          <t>Nitto EE-1010 TH6 6mm</t>
+        </is>
+      </c>
+      <c r="C381" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D381" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E381" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F381" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G381" s="86" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="H381" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I381" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J381" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K381" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2897</t>
+        </is>
+      </c>
+      <c r="L381" s="33" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B382" s="29" t="inlineStr">
+        <is>
+          <t>Nitto EE1010 20mm</t>
+        </is>
+      </c>
+      <c r="C382" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D382" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E382" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F382" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G382" s="86" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="H382" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I382" s="28" t="inlineStr">
+        <is>
+          <t>4 role</t>
+        </is>
+      </c>
+      <c r="J382" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K382" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2897</t>
+        </is>
+      </c>
+      <c r="L382" s="33" t="inlineStr">
+        <is>
+          <t>DDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B383" s="29" t="inlineStr">
+        <is>
+          <t>Nitto EE1010 28mm</t>
+        </is>
+      </c>
+      <c r="C383" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D383" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E383" s="28" t="n">
+        <v>28</v>
+      </c>
+      <c r="F383" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G383" s="86" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H383" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I383" s="28" t="inlineStr">
+        <is>
+          <t>3 cutii</t>
+        </is>
+      </c>
+      <c r="J383" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K383" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2897</t>
+        </is>
+      </c>
+      <c r="L383" s="33" t="inlineStr">
+        <is>
+          <t>DDP; 10 sheets/box</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B384" s="29" t="inlineStr">
+        <is>
+          <t>3M™ VHB™ 5952F</t>
+        </is>
+      </c>
+      <c r="C384" s="28" t="n">
+        <v>1220</v>
+      </c>
+      <c r="D384" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E384" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F384" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G384" s="86" t="n">
+        <v>73</v>
+      </c>
+      <c r="H384" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I384" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J384" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K384" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2893 Volvo</t>
+        </is>
+      </c>
+      <c r="L384" s="33" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B385" s="29" t="inlineStr">
+        <is>
+          <t>EC-210 12mm</t>
+        </is>
+      </c>
+      <c r="C385" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D385" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E385" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="F385" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G385" s="86" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="H385" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I385" s="28" t="inlineStr">
+        <is>
+          <t>6 cutii</t>
+        </is>
+      </c>
+      <c r="J385" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K385" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2849</t>
+        </is>
+      </c>
+      <c r="L385" s="33" t="inlineStr">
+        <is>
+          <t>alt. la EE1010; LT 14 sapt</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B386" s="29" t="inlineStr">
+        <is>
+          <t>BASOTECT E G+ laminat PU</t>
+        </is>
+      </c>
+      <c r="C386" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D386" s="28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E386" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F386" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G386" s="86" t="n">
+        <v>14</v>
+      </c>
+      <c r="H386" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I386" s="28" t="inlineStr">
+        <is>
+          <t>50 mp</t>
+        </is>
+      </c>
+      <c r="J386" s="31" t="inlineStr">
+        <is>
+          <t>BASF</t>
+        </is>
+      </c>
+      <c r="K386" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2892</t>
+        </is>
+      </c>
+      <c r="L386" s="33" t="inlineStr">
+        <is>
+          <t>laminat cu PU film</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B387" s="29" t="inlineStr">
+        <is>
+          <t>Role EPDM-L 5mm</t>
+        </is>
+      </c>
+      <c r="C387" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D387" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E387" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F387" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G387" s="86" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H387" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I387" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J387" s="31" t="inlineStr">
+        <is>
+          <t>Koepp</t>
+        </is>
+      </c>
+      <c r="K387" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2756</t>
+        </is>
+      </c>
+      <c r="L387" s="33" t="inlineStr">
+        <is>
+          <t>EXW; 20m×1000×5mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B388" s="29" t="inlineStr">
+        <is>
+          <t>Nitto EE1000 15mm</t>
+        </is>
+      </c>
+      <c r="C388" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D388" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E388" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="F388" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G388" s="86" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="H388" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I388" s="28" t="inlineStr">
+        <is>
+          <t>2 paleti</t>
+        </is>
+      </c>
+      <c r="J388" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K388" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2786</t>
+        </is>
+      </c>
+      <c r="L388" s="33" t="inlineStr">
+        <is>
+          <t>DDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B389" s="29" t="inlineStr">
+        <is>
+          <t>3M™ VHB™ Tape Max-110GF Grey 1.1mm</t>
+        </is>
+      </c>
+      <c r="C389" s="28" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D389" s="28" t="n">
+        <v>33</v>
+      </c>
+      <c r="E389" s="28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F389" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G389" s="86" t="n">
+        <v>79</v>
+      </c>
+      <c r="H389" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I389" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J389" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K389" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2896 Renault</t>
+        </is>
+      </c>
+      <c r="L389" s="33" t="inlineStr">
+        <is>
+          <t>VHB MAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B390" s="29" t="inlineStr">
+        <is>
+          <t>EPDM S ES0100 Shore A70 4mm</t>
+        </is>
+      </c>
+      <c r="C390" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D390" s="28" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E390" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F390" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G390" s="86" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="H390" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I390" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J390" s="31" t="inlineStr"/>
+      <c r="K390" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2849</t>
+        </is>
+      </c>
+      <c r="L390" s="33" t="inlineStr">
+        <is>
+          <t>1000×1400×4mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B391" s="29" t="inlineStr">
+        <is>
+          <t>EPDM S ES0200 Shore A60 4mm</t>
+        </is>
+      </c>
+      <c r="C391" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D391" s="28" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E391" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F391" s="28" t="inlineStr">
+        <is>
+          <t>plăci</t>
+        </is>
+      </c>
+      <c r="G391" s="86" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="H391" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I391" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J391" s="31" t="inlineStr"/>
+      <c r="K391" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2849</t>
+        </is>
+      </c>
+      <c r="L391" s="33" t="inlineStr">
+        <is>
+          <t>1000×1400×4mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B392" s="29" t="inlineStr">
+        <is>
+          <t>Role Koepp EPDM-SUW 1mm</t>
+        </is>
+      </c>
+      <c r="C392" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D392" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E392" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F392" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G392" s="86" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H392" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I392" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J392" s="31" t="inlineStr">
+        <is>
+          <t>Koepp</t>
+        </is>
+      </c>
+      <c r="K392" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2900</t>
+        </is>
+      </c>
+      <c r="L392" s="33" t="inlineStr">
+        <is>
+          <t>DIN 7715 P3; 20m×1000×1mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B393" s="29" t="inlineStr">
+        <is>
+          <t>Nitto DCT5000NS</t>
+        </is>
+      </c>
+      <c r="C393" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D393" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E393" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F393" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G393" s="86" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H393" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I393" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J393" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K393" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2900</t>
+        </is>
+      </c>
+      <c r="L393" s="33" t="inlineStr">
+        <is>
+          <t>DDP; air freight Japan</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B394" s="29" t="inlineStr">
+        <is>
+          <t>Nitto 579008 0.9mm</t>
+        </is>
+      </c>
+      <c r="C394" s="28" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D394" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E394" s="28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F394" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G394" s="86" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="H394" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I394" s="28" t="inlineStr">
+        <is>
+          <t>6 logrole</t>
+        </is>
+      </c>
+      <c r="J394" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K394" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2900</t>
+        </is>
+      </c>
+      <c r="L394" s="33" t="inlineStr">
+        <is>
+          <t>DDP; untrimmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B395" s="29" t="inlineStr">
+        <is>
+          <t>P03055B BLUE SILICONE cu liner</t>
+        </is>
+      </c>
+      <c r="C395" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="D395" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E395" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F395" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G395" s="86" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H395" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I395" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J395" s="31" t="inlineStr"/>
+      <c r="K395" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2320</t>
+        </is>
+      </c>
+      <c r="L395" s="33" t="inlineStr">
+        <is>
+          <t>recalculat</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B396" s="29" t="inlineStr">
+        <is>
+          <t>BANDA ADEZIVA GRAND GREEN</t>
+        </is>
+      </c>
+      <c r="C396" s="28" t="n">
+        <v>48</v>
+      </c>
+      <c r="D396" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E396" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F396" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G396" s="86" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H396" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I396" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J396" s="31" t="inlineStr"/>
+      <c r="K396" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2320</t>
+        </is>
+      </c>
+      <c r="L396" s="33" t="inlineStr">
+        <is>
+          <t>recalculat; diverse culori</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B397" s="29" t="inlineStr">
+        <is>
+          <t>kSil FR50 2mm</t>
+        </is>
+      </c>
+      <c r="C397" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D397" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E397" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F397" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G397" s="86" t="n">
+        <v>74</v>
+      </c>
+      <c r="H397" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I397" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J397" s="31" t="inlineStr"/>
+      <c r="K397" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2889 Eckerle</t>
+        </is>
+      </c>
+      <c r="L397" s="33" t="inlineStr">
+        <is>
+          <t>flame retardant; +adeziv 86</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B398" s="29" t="inlineStr">
+        <is>
+          <t>kSil FR50 3mm</t>
+        </is>
+      </c>
+      <c r="C398" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D398" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E398" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F398" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G398" s="86" t="n">
+        <v>98</v>
+      </c>
+      <c r="H398" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I398" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J398" s="31" t="inlineStr"/>
+      <c r="K398" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2889 Eckerle</t>
+        </is>
+      </c>
+      <c r="L398" s="33" t="inlineStr">
+        <is>
+          <t>+adeziv 110</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B399" s="29" t="inlineStr">
+        <is>
+          <t>kSil FR50 8mm</t>
+        </is>
+      </c>
+      <c r="C399" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D399" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E399" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F399" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G399" s="86" t="n">
+        <v>209</v>
+      </c>
+      <c r="H399" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I399" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J399" s="31" t="inlineStr"/>
+      <c r="K399" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2889 Eckerle</t>
+        </is>
+      </c>
+      <c r="L399" s="33" t="inlineStr">
+        <is>
+          <t>+adeziv 221</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B400" s="29" t="inlineStr">
+        <is>
+          <t>FELT SIDMER 500G/SQM-10 alb</t>
+        </is>
+      </c>
+      <c r="C400" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D400" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E400" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F400" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G400" s="86" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H400" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I400" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J400" s="31" t="inlineStr"/>
+      <c r="K400" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2903 Classfurn</t>
+        </is>
+      </c>
+      <c r="L400" s="33" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B401" s="29" t="inlineStr">
+        <is>
+          <t>BANDA S-4710 AG</t>
+        </is>
+      </c>
+      <c r="C401" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D401" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="E401" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F401" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G401" s="86" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H401" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I401" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J401" s="31" t="inlineStr">
+        <is>
+          <t>Neveon</t>
+        </is>
+      </c>
+      <c r="K401" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2903 Classfurn</t>
+        </is>
+      </c>
+      <c r="L401" s="33" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:L120">

--- a/MDE_Materii_Prime_Preturi.xlsx
+++ b/MDE_Materii_Prime_Preturi.xlsx
@@ -1148,7 +1148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L401"/>
+  <dimension ref="A1:L411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="140" min="1" max="1"/>
@@ -22417,7 +22417,7 @@
       </c>
       <c r="L400" s="33" t="inlineStr"/>
     </row>
-    <row r="401">
+    <row r="401" s="140">
       <c r="A401" s="28" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -22468,6 +22468,548 @@
         </is>
       </c>
       <c r="L401" s="33" t="inlineStr"/>
+    </row>
+    <row r="402" s="140">
+      <c r="A402" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B402" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Acrylic Plus Tape EX4011 Black 1.1mm</t>
+        </is>
+      </c>
+      <c r="C402" s="28" t="n">
+        <v>1220</v>
+      </c>
+      <c r="D402" s="28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E402" s="28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F402" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G402" s="86" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="H402" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I402" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J402" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K402" s="32" t="inlineStr">
+        <is>
+          <t>Optimatriks (EX4011 4mm × 33m)</t>
+        </is>
+      </c>
+      <c r="L402" s="33" t="inlineStr">
+        <is>
+          <t>material din stoc MDE; ofertă FCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" s="140">
+      <c r="A403" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B403" s="29" t="inlineStr">
+        <is>
+          <t>EPDM 71-42 5mm</t>
+        </is>
+      </c>
+      <c r="C403" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D403" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E403" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F403" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G403" s="86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H403" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I403" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J403" s="31" t="inlineStr">
+        <is>
+          <t>Interep</t>
+        </is>
+      </c>
+      <c r="K403" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2756</t>
+        </is>
+      </c>
+      <c r="L403" s="33" t="inlineStr">
+        <is>
+          <t>grosime 5 ±0.5mm; ofertă nouă Interep</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" s="140">
+      <c r="A404" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B404" s="29" t="inlineStr">
+        <is>
+          <t>3M™ Thinsulate TF1800 ACST 27708</t>
+        </is>
+      </c>
+      <c r="C404" s="28" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D404" s="28" t="n">
+        <v>160</v>
+      </c>
+      <c r="E404" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F404" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G404" s="86" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H404" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I404" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J404" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="K404" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2912 Adler Pelzer GWM EC15</t>
+        </is>
+      </c>
+      <c r="L404" s="33" t="inlineStr">
+        <is>
+          <t>SAP 7100285433; 243.2 mp/rolă; grilă preț 3M 2023 RO</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" s="140">
+      <c r="A405" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B405" s="29" t="inlineStr">
+        <is>
+          <t>Airlite AM1502</t>
+        </is>
+      </c>
+      <c r="C405" s="28" t="n">
+        <v>1520</v>
+      </c>
+      <c r="D405" s="28" t="n">
+        <v>190</v>
+      </c>
+      <c r="E405" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F405" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G405" s="86" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H405" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I405" s="28" t="inlineStr">
+        <is>
+          <t>1 TIR / 40 role</t>
+        </is>
+      </c>
+      <c r="J405" s="31" t="n"/>
+      <c r="K405" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2912 Adler Pelzer GWM EC15</t>
+        </is>
+      </c>
+      <c r="L405" s="33" t="inlineStr">
+        <is>
+          <t>DAP Oltenița; furnizor nespecificat în mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" s="140">
+      <c r="A406" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B406" s="29" t="inlineStr">
+        <is>
+          <t>BANDA S4707MF ATP</t>
+        </is>
+      </c>
+      <c r="C406" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D406" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="E406" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F406" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G406" s="86" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H406" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I406" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J406" s="31" t="inlineStr">
+        <is>
+          <t>ATP</t>
+        </is>
+      </c>
+      <c r="K406" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2913 Adler Pelzer GWM EC15</t>
+        </is>
+      </c>
+      <c r="L406" s="33" t="n"/>
+    </row>
+    <row r="407" s="140">
+      <c r="A407" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B407" s="29" t="inlineStr">
+        <is>
+          <t>NITTO 5015T</t>
+        </is>
+      </c>
+      <c r="C407" s="28" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D407" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="E407" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F407" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G407" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="H407" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I407" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J407" s="31" t="inlineStr">
+        <is>
+          <t>Nitto</t>
+        </is>
+      </c>
+      <c r="K407" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2913 Adler Pelzer GWM EC15</t>
+        </is>
+      </c>
+      <c r="L407" s="33" t="n"/>
+    </row>
+    <row r="408" s="140">
+      <c r="A408" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B408" s="29" t="inlineStr">
+        <is>
+          <t>FELT HDF B4794 60G/M2 (PES 60)</t>
+        </is>
+      </c>
+      <c r="C408" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D408" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E408" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F408" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G408" s="86" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H408" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I408" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J408" s="31" t="inlineStr">
+        <is>
+          <t>Filc RO</t>
+        </is>
+      </c>
+      <c r="K408" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2913 Adler Pelzer GWM EC15</t>
+        </is>
+      </c>
+      <c r="L408" s="33" t="n"/>
+    </row>
+    <row r="409" s="140">
+      <c r="A409" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B409" s="29" t="inlineStr">
+        <is>
+          <t>ENVIZOL TB 1200 WHITE (PET felt)</t>
+        </is>
+      </c>
+      <c r="C409" s="28" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D409" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E409" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="F409" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G409" s="86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H409" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I409" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J409" s="31" t="inlineStr">
+        <is>
+          <t>Retex</t>
+        </is>
+      </c>
+      <c r="K409" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2911 Adler Pelzer GWM EC15</t>
+        </is>
+      </c>
+      <c r="L409" s="33" t="inlineStr">
+        <is>
+          <t>1200 g/mp, alb; UM nespecificată în mail (presupus €/mp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" s="140">
+      <c r="A410" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B410" s="29" t="inlineStr">
+        <is>
+          <t>ENVIZOL TB SA 600 WHITE</t>
+        </is>
+      </c>
+      <c r="C410" s="28" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D410" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E410" s="28" t="inlineStr">
+        <is>
+          <t>10-15</t>
+        </is>
+      </c>
+      <c r="F410" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G410" s="86" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H410" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I410" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J410" s="31" t="inlineStr">
+        <is>
+          <t>Retex</t>
+        </is>
+      </c>
+      <c r="K410" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2912 Adler Pelzer GWM EC15</t>
+        </is>
+      </c>
+      <c r="L410" s="33" t="inlineStr">
+        <is>
+          <t>600 g/mp, alb, autoadeziv</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" s="140">
+      <c r="A411" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B411" s="29" t="inlineStr">
+        <is>
+          <t>FELT PES SA 150 BLACK</t>
+        </is>
+      </c>
+      <c r="C411" s="28" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D411" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E411" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F411" s="28" t="inlineStr">
+        <is>
+          <t>rolă</t>
+        </is>
+      </c>
+      <c r="G411" s="86" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H411" s="28" t="inlineStr">
+        <is>
+          <t>€/mp</t>
+        </is>
+      </c>
+      <c r="I411" s="28" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J411" s="31" t="inlineStr">
+        <is>
+          <t>Retex</t>
+        </is>
+      </c>
+      <c r="K411" s="32" t="inlineStr">
+        <is>
+          <t>PRJ 2913 Adler Pelzer GWM EC15</t>
+        </is>
+      </c>
+      <c r="L411" s="33" t="inlineStr">
+        <is>
+          <t>150 g/mp, negru, autoadeziv; preț considerat mare de Purchasing</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:L120">
